--- a/Result/profitability/1777.xlsx
+++ b/Result/profitability/1777.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.66</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5975</v>
+        <v>1.52625</v>
       </c>
       <c r="N2" t="n">
-        <v>37.11375</v>
+        <v>38.265</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.85</v>
       </c>
       <c r="M3" t="n">
-        <v>1.37875</v>
+        <v>1.37625</v>
       </c>
       <c r="N3" t="n">
-        <v>38.11499999999999</v>
+        <v>38.1925</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.53</v>
       </c>
       <c r="M4" t="n">
-        <v>1.18875</v>
+        <v>1.23</v>
       </c>
       <c r="N4" t="n">
-        <v>38.1225</v>
+        <v>38.76375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0175</v>
+        <v>1.225</v>
       </c>
       <c r="N5" t="n">
-        <v>38.34125</v>
+        <v>40.04125000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.73</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0625</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>38.9825</v>
+        <v>40.14625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0.93375</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>39.86</v>
+        <v>40.01125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.34</v>
       </c>
       <c r="M8" t="n">
-        <v>0.71875</v>
+        <v>0.7712499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>39.7175</v>
+        <v>39.92250000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,10 +1645,10 @@
         <v>0.77</v>
       </c>
       <c r="M10" t="n">
-        <v>0.58625</v>
+        <v>0.5862499999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>38.3825</v>
+        <v>38.38250000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6375</v>
+        <v>0.6375000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>38.62375</v>
@@ -1899,10 +1899,10 @@
         <v>0.79</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6699999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="N12" t="n">
-        <v>38.22875000000001</v>
+        <v>38.22875</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1777</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>336</v>
+      </c>
+      <c r="D75" t="n">
+        <v>195</v>
+      </c>
+      <c r="E75" t="n">
+        <v>141</v>
+      </c>
+      <c r="F75" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="G75" t="n">
+        <v>105</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>31.30%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>116</v>
+      </c>
+      <c r="K75" t="n">
+        <v>91</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.76875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.4199999999999997</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2608695652173911</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.640000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.04064436183395292</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.486486486486486</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4790419161676647</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
